--- a/Assets/Data/Excel/Consumables.xlsx
+++ b/Assets/Data/Excel/Consumables.xlsx
@@ -288,9 +288,9 @@
         </is>
       </x:c>
       <x:c r="C2" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>범위 내 아군의 체력을 각각 80 회복합니다.</t>
-        </is>
+        <x:is>
+          <x:t>범위 내 아군의 체력을 각각 65 회복합니다.</x:t>
+        </x:is>
       </x:c>
       <x:c r="D2" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -302,10 +302,8 @@
           <t>Area</t>
         </is>
       </x:c>
-      <x:c r="F2" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>3</t>
-        </is>
+      <x:c r="F2">
+        <x:v>3.5</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -384,9 +382,9 @@
         </is>
       </x:c>
       <x:c r="C5" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>6초 동안 범위 내 적의 공격력이 20% 감소합니다.</t>
-        </is>
+        <x:is>
+          <x:t>6초 동안 범위 내 적의 공격력이 12% 감소합니다.</x:t>
+        </x:is>
       </x:c>
       <x:c r="D5" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -398,10 +396,8 @@
           <t>Area</t>
         </is>
       </x:c>
-      <x:c r="F5" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>3</t>
-        </is>
+      <x:c r="F5">
+        <x:v>4.5</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -416,9 +412,9 @@
         </is>
       </x:c>
       <x:c r="C6" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>6초 동안 범위 내 아군이 2초마다 각자의 최대 체력의 3%를 회복합니다.</t>
-        </is>
+        <x:is>
+          <x:t>6초 동안 범위 내 아군이 2초마다 각자의 최대 체력의 2%를 회복합니다.</x:t>
+        </x:is>
       </x:c>
       <x:c r="D6" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -430,10 +426,8 @@
           <t>Area</t>
         </is>
       </x:c>
-      <x:c r="F6" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>3</t>
-        </is>
+      <x:c r="F6">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -512,9 +506,9 @@
         </is>
       </x:c>
       <x:c r="C9" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>6초 동안 범위 내 아군의 방어력이 20% 증가합니다.</t>
-        </is>
+        <x:is>
+          <x:t>6초 동안 범위 내 아군의 방어력이 15% 증가합니다.</x:t>
+        </x:is>
       </x:c>
       <x:c r="D9" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -526,10 +520,8 @@
           <t>Area</t>
         </is>
       </x:c>
-      <x:c r="F9" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>3</t>
-        </is>
+      <x:c r="F9">
+        <x:v>3.5</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -544,9 +536,9 @@
         </is>
       </x:c>
       <x:c r="C10" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>5초 동안 범위 내 아군의 받는 피해 배율이 10% 감소합니다.</t>
-        </is>
+        <x:is>
+          <x:t>5초 동안 범위 내 아군의 받는 피해 배율이 8% 감소합니다.</x:t>
+        </x:is>
       </x:c>
       <x:c r="D10" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -558,10 +550,8 @@
           <t>Area</t>
         </is>
       </x:c>
-      <x:c r="F10" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>3</t>
-        </is>
+      <x:c r="F10">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -608,9 +598,9 @@
         </is>
       </x:c>
       <x:c r="C12" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>6초 동안 범위 내 아군의 치명타 확률이 8%p 증가합니다.</t>
-        </is>
+        <x:is>
+          <x:t>6초 동안 범위 내 아군의 치명타 확률이 8% 증가합니다.</x:t>
+        </x:is>
       </x:c>
       <x:c r="D12" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -640,9 +630,9 @@
         </is>
       </x:c>
       <x:c r="C13" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>6초 동안 범위 내 아군의 방어력 무시 비율이 8%p 증가합니다.</t>
-        </is>
+        <x:is>
+          <x:t>6초 동안 범위 내 아군의 방어력 무시 비율이 8% 증가합니다.</x:t>
+        </x:is>
       </x:c>
       <x:c r="D13" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -655,38 +645,6 @@
         </is>
       </x:c>
       <x:c r="F13" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>3</t>
-        </is>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>consumable_013</t>
-        </is>
-      </x:c>
-      <x:c r="B14" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>흡혈의 향로</t>
-        </is>
-      </x:c>
-      <x:c r="C14" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>6초 동안 범위 내 아군의 흡혈 비율이 3%p 증가합니다.</t>
-        </is>
-      </x:c>
-      <x:c r="D14" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>Ally</t>
-        </is>
-      </x:c>
-      <x:c r="E14" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>Area</t>
-        </is>
-      </x:c>
-      <x:c r="F14" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
           <t>3</t>
         </is>
@@ -736,9 +694,9 @@
         </is>
       </x:c>
       <x:c r="C16" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>범위 내 적에게 기본 마법 피해 100을 줍니다.</t>
-        </is>
+        <x:is>
+          <x:t>범위 내 적에게 기본 마법 피해 80을 줍니다.</x:t>
+        </x:is>
       </x:c>
       <x:c r="D16" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -750,10 +708,8 @@
           <t>Area</t>
         </is>
       </x:c>
-      <x:c r="F16" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>3</t>
-        </is>
+      <x:c r="F16">
+        <x:v>3.5</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -800,9 +756,9 @@
         </is>
       </x:c>
       <x:c r="C18" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>5초 동안 범위 내 적의 이동속도가 25% 감소합니다.</t>
-        </is>
+        <x:is>
+          <x:t>5초 동안 범위 내 적의 이동속도가 18% 감소합니다.</x:t>
+        </x:is>
       </x:c>
       <x:c r="D18" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -814,10 +770,8 @@
           <t>Area</t>
         </is>
       </x:c>
-      <x:c r="F18" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>3</t>
-        </is>
+      <x:c r="F18">
+        <x:v>4.5</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -896,9 +850,9 @@
         </is>
       </x:c>
       <x:c r="C21" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>6초 동안 범위 내 적에게 1초마다 기본 지속 피해 15를 줍니다.</t>
-        </is>
+        <x:is>
+          <x:t>6초 동안 범위 내 적에게 1초마다 기본 지속 피해 12를 줍니다.</x:t>
+        </x:is>
       </x:c>
       <x:c r="D21" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -910,10 +864,8 @@
           <t>Area</t>
         </is>
       </x:c>
-      <x:c r="F21" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>3</t>
-        </is>
+      <x:c r="F21">
+        <x:v>3.5</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -1243,10 +1195,8 @@
           <t>Heal</t>
         </is>
       </x:c>
-      <x:c r="C2" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>80</t>
-        </is>
+      <x:c r="C2">
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D2" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -1488,26 +1438,6 @@
         </is>
       </x:c>
     </x:row>
-    <x:row r="14">
-      <x:c r="A14" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>consumable_013</t>
-        </is>
-      </x:c>
-      <x:c r="B14" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>Runtime</t>
-        </is>
-      </x:c>
-      <x:c r="C14"/>
-      <x:c r="D14"/>
-      <x:c r="E14"/>
-      <x:c r="F14" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>consumable_VampiricCenserEffect</t>
-        </is>
-      </x:c>
-    </x:row>
     <x:row r="15">
       <x:c r="A15" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -1539,10 +1469,8 @@
           <t>Damage</t>
         </is>
       </x:c>
-      <x:c r="C16" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>100</t>
-        </is>
+      <x:c r="C16">
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D16"/>
       <x:c r="E16" t="inlineStr">
@@ -2132,38 +2060,6 @@
         </is>
       </x:c>
     </x:row>
-    <x:row r="10">
-      <x:c r="A10" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>consumable_VampiricCenserEffect</t>
-        </is>
-      </x:c>
-      <x:c r="B10" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>Beneficial</t>
-        </is>
-      </x:c>
-      <x:c r="C10" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>Timed</t>
-        </is>
-      </x:c>
-      <x:c r="D10" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>6</t>
-        </is>
-      </x:c>
-      <x:c r="E10" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>Refresh</t>
-        </is>
-      </x:c>
-      <x:c r="F10" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>1</t>
-        </is>
-      </x:c>
-    </x:row>
     <x:row r="11">
       <x:c r="A11" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -2687,10 +2583,8 @@
           <t>Percent</t>
         </is>
       </x:c>
-      <x:c r="E3" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>-0.2</t>
-        </is>
+      <x:c r="E3">
+        <x:v>-0.12</x:v>
       </x:c>
       <x:c r="F3"/>
       <x:c r="G3"/>
@@ -2708,10 +2602,8 @@
       </x:c>
       <x:c r="C4"/>
       <x:c r="D4"/>
-      <x:c r="E4" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>0.03</t>
-        </is>
+      <x:c r="E4">
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="F4" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -2741,10 +2633,8 @@
           <t>Percent</t>
         </is>
       </x:c>
-      <x:c r="E5" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>0.2</t>
-        </is>
+      <x:c r="E5">
+        <x:v>0.15</x:v>
       </x:c>
       <x:c r="F5"/>
       <x:c r="G5"/>
@@ -2770,10 +2660,8 @@
           <t>Percent</t>
         </is>
       </x:c>
-      <x:c r="E6" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>-0.1</t>
-        </is>
+      <x:c r="E6">
+        <x:v>-0.08</x:v>
       </x:c>
       <x:c r="F6"/>
       <x:c r="G6"/>
@@ -2865,35 +2753,6 @@
       <x:c r="F9"/>
       <x:c r="G9"/>
     </x:row>
-    <x:row r="10">
-      <x:c r="A10" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>consumable_VampiricCenserEffect</t>
-        </is>
-      </x:c>
-      <x:c r="B10" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>Stat</t>
-        </is>
-      </x:c>
-      <x:c r="C10" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>LifeSteal</t>
-        </is>
-      </x:c>
-      <x:c r="D10" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>Flat</t>
-        </is>
-      </x:c>
-      <x:c r="E10" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>0.03</t>
-        </is>
-      </x:c>
-      <x:c r="F10"/>
-      <x:c r="G10"/>
-    </x:row>
     <x:row r="11">
       <x:c r="A11" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -2973,10 +2832,8 @@
           <t>Percent</t>
         </is>
       </x:c>
-      <x:c r="E13" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>-0.25</t>
-        </is>
+      <x:c r="E13">
+        <x:v>-0.18</x:v>
       </x:c>
       <x:c r="F13"/>
       <x:c r="G13"/>
@@ -3036,10 +2893,8 @@
       </x:c>
       <x:c r="C16"/>
       <x:c r="D16"/>
-      <x:c r="E16" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>15</t>
-        </is>
+      <x:c r="E16">
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F16" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">

--- a/Assets/Data/Excel/Consumables.xlsx
+++ b/Assets/Data/Excel/Consumables.xlsx
@@ -289,7 +289,7 @@
       </x:c>
       <x:c r="C2" t="inlineStr">
         <x:is>
-          <x:t>범위 내 아군의 체력을 각각 65 회복합니다.</x:t>
+          <x:t>범위 내 아군의 체력을 각각 220 회복</x:t>
         </x:is>
       </x:c>
       <x:c r="D2" t="inlineStr">
@@ -318,9 +318,9 @@
         </is>
       </x:c>
       <x:c r="C3" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>범위 내 적에게 기본 물리 피해 100을 줍니다.</t>
-        </is>
+        <x:is>
+          <x:t>범위 내 적에게 기본 물리 피해 300</x:t>
+        </x:is>
       </x:c>
       <x:c r="D3" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -350,9 +350,9 @@
         </is>
       </x:c>
       <x:c r="C4" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>6초 동안 모든 아군의 공격속도가 10% 증가합니다.</t>
-        </is>
+        <x:is>
+          <x:t>8초 동안 모든 아군의 공격속도가 15% 증가</x:t>
+        </x:is>
       </x:c>
       <x:c r="D4" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -383,7 +383,7 @@
       </x:c>
       <x:c r="C5" t="inlineStr">
         <x:is>
-          <x:t>6초 동안 범위 내 적의 공격력이 12% 감소합니다.</x:t>
+          <x:t>6초 동안 범위 내 적의 공격력이 20% 감소</x:t>
         </x:is>
       </x:c>
       <x:c r="D5" t="inlineStr">
@@ -413,7 +413,7 @@
       </x:c>
       <x:c r="C6" t="inlineStr">
         <x:is>
-          <x:t>6초 동안 범위 내 아군이 2초마다 각자의 최대 체력의 2%를 회복합니다.</x:t>
+          <x:t>6초 동안 범위 내 아군이 2초마다 최대 체력의 4% 회복</x:t>
         </x:is>
       </x:c>
       <x:c r="D6" t="inlineStr">
@@ -442,9 +442,9 @@
         </is>
       </x:c>
       <x:c r="C7" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>모든 아군의 체력을 각각 40 회복합니다.</t>
-        </is>
+        <x:is>
+          <x:t>모든 아군의 체력을 각각 120 회복</x:t>
+        </x:is>
       </x:c>
       <x:c r="D7" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -474,9 +474,9 @@
         </is>
       </x:c>
       <x:c r="C8" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>범위 내 아군에게 각각 보호막 80을 부여합니다.</t>
-        </is>
+        <x:is>
+          <x:t>범위 내 아군에게 각각 보호막 250 부여</x:t>
+        </x:is>
       </x:c>
       <x:c r="D8" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -507,7 +507,7 @@
       </x:c>
       <x:c r="C9" t="inlineStr">
         <x:is>
-          <x:t>6초 동안 범위 내 아군의 방어력이 15% 증가합니다.</x:t>
+          <x:t>6초 동안 범위 내 아군의 방어력이 10 증가</x:t>
         </x:is>
       </x:c>
       <x:c r="D9" t="inlineStr">
@@ -537,7 +537,7 @@
       </x:c>
       <x:c r="C10" t="inlineStr">
         <x:is>
-          <x:t>5초 동안 범위 내 아군의 받는 피해 배율이 8% 감소합니다.</x:t>
+          <x:t>5초 동안 범위 내 아군의 받는 피해 배율이 18% 감소</x:t>
         </x:is>
       </x:c>
       <x:c r="D10" t="inlineStr">
@@ -566,9 +566,9 @@
         </is>
       </x:c>
       <x:c r="C11" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>6초 동안 모든 아군의 공격력이 10% 증가합니다.</t>
-        </is>
+        <x:is>
+          <x:t>8초 동안 모든 아군의 공격력이 15% 증가</x:t>
+        </x:is>
       </x:c>
       <x:c r="D11" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -599,7 +599,7 @@
       </x:c>
       <x:c r="C12" t="inlineStr">
         <x:is>
-          <x:t>6초 동안 범위 내 아군의 치명타 확률이 8% 증가합니다.</x:t>
+          <x:t>8초 동안 범위 내 아군의 치명타 확률이 20% 증가</x:t>
         </x:is>
       </x:c>
       <x:c r="D12" t="inlineStr">
@@ -631,7 +631,7 @@
       </x:c>
       <x:c r="C13" t="inlineStr">
         <x:is>
-          <x:t>6초 동안 범위 내 아군의 방어력 무시 비율이 8% 증가합니다.</x:t>
+          <x:t>8초 동안 범위 내 아군의 방어력 무시 비율이 30% 증가</x:t>
         </x:is>
       </x:c>
       <x:c r="D13" t="inlineStr">
@@ -662,9 +662,9 @@
         </is>
       </x:c>
       <x:c r="C15" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>6초 동안 모든 아군의 이동속도가 15% 증가합니다.</t>
-        </is>
+        <x:is>
+          <x:t>8초 동안 모든 아군의 이동속도가 30% 증가</x:t>
+        </x:is>
       </x:c>
       <x:c r="D15" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -695,7 +695,7 @@
       </x:c>
       <x:c r="C16" t="inlineStr">
         <x:is>
-          <x:t>범위 내 적에게 기본 마법 피해 80을 줍니다.</x:t>
+          <x:t>범위 내 적에게 기본 마법 피해 240</x:t>
         </x:is>
       </x:c>
       <x:c r="D16" t="inlineStr">
@@ -724,9 +724,9 @@
         </is>
       </x:c>
       <x:c r="C17" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>6초 동안 범위 내 적의 방어력이 20% 감소합니다.</t>
-        </is>
+        <x:is>
+          <x:t>6초 동안 범위 내 적의 방어력이 35% 감소</x:t>
+        </x:is>
       </x:c>
       <x:c r="D17" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -757,7 +757,7 @@
       </x:c>
       <x:c r="C18" t="inlineStr">
         <x:is>
-          <x:t>5초 동안 범위 내 적의 이동속도가 18% 감소합니다.</x:t>
+          <x:t>6초 동안 범위 내 적의 이동속도가 30% 감소</x:t>
         </x:is>
       </x:c>
       <x:c r="D18" t="inlineStr">
@@ -786,9 +786,9 @@
         </is>
       </x:c>
       <x:c r="C19" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>범위 내 적을 1초 동안 기절시킵니다.</t>
-        </is>
+        <x:is>
+          <x:t>범위 내 적을 1.25초 동안 기절</x:t>
+        </x:is>
       </x:c>
       <x:c r="D19" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -818,9 +818,9 @@
         </is>
       </x:c>
       <x:c r="C20" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>범위 내 적을 2초 동안 침묵시킵니다.</t>
-        </is>
+        <x:is>
+          <x:t>범위 내 적을 2.5초 동안 침묵</x:t>
+        </x:is>
       </x:c>
       <x:c r="D20" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -851,7 +851,7 @@
       </x:c>
       <x:c r="C21" t="inlineStr">
         <x:is>
-          <x:t>6초 동안 범위 내 적에게 1초마다 기본 지속 피해 12를 줍니다.</x:t>
+          <x:t>6초 동안 범위 내 적에게 1초마다 기본 지속 피해 60</x:t>
         </x:is>
       </x:c>
       <x:c r="D21" t="inlineStr">
@@ -880,9 +880,9 @@
         </is>
       </x:c>
       <x:c r="C22" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>범위 내 적을 1.5초 동안 속박합니다.</t>
-        </is>
+        <x:is>
+          <x:t>범위 내 적을 2.5초 동안 속박</x:t>
+        </x:is>
       </x:c>
       <x:c r="D22" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -912,9 +912,9 @@
         </is>
       </x:c>
       <x:c r="C23" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>모든 적에게 기본 마법 피해 40을 줍니다.</t>
-        </is>
+        <x:is>
+          <x:t>모든 적에게 기본 마법 피해 120</x:t>
+        </x:is>
       </x:c>
       <x:c r="D23" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -944,9 +944,9 @@
         </is>
       </x:c>
       <x:c r="C24" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>5초 동안 모든 적의 공격력이 10% 감소합니다.</t>
-        </is>
+        <x:is>
+          <x:t>5초 동안 모든 적의 공격력이 15% 감소</x:t>
+        </x:is>
       </x:c>
       <x:c r="D24" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -976,9 +976,9 @@
         </is>
       </x:c>
       <x:c r="C25" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>5초 동안 모든 적의 방어력이 10% 감소합니다.</t>
-        </is>
+        <x:is>
+          <x:t>5초 동안 모든 적의 방어력이 20% 감소</x:t>
+        </x:is>
       </x:c>
       <x:c r="D25" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -1008,9 +1008,9 @@
         </is>
       </x:c>
       <x:c r="C26" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>4초 동안 모든 적의 이동속도가 15% 감소합니다.</t>
-        </is>
+        <x:is>
+          <x:t>5초 동안 모든 적의 이동속도가 25% 감소</x:t>
+        </x:is>
       </x:c>
       <x:c r="D26" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -1040,9 +1040,9 @@
         </is>
       </x:c>
       <x:c r="C27" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>5초 동안 모든 적의 공격속도가 10% 감소합니다.</t>
-        </is>
+        <x:is>
+          <x:t>5초 동안 모든 적의 공격속도가 15% 감소</x:t>
+        </x:is>
       </x:c>
       <x:c r="D27" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -1072,9 +1072,9 @@
         </is>
       </x:c>
       <x:c r="C28" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>모든 적을 1초 동안 침묵시킵니다.</t>
-        </is>
+        <x:is>
+          <x:t>모든 적을 1.25초 동안 침묵</x:t>
+        </x:is>
       </x:c>
       <x:c r="D28" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -1104,9 +1104,9 @@
         </is>
       </x:c>
       <x:c r="C29" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>6초 동안 모든 적에게 2초마다 기본 지속 피해 10을 줍니다.</t>
-        </is>
+        <x:is>
+          <x:t>6초 동안 모든 적에게 2초마다 기본 지속 피해 60</x:t>
+        </x:is>
       </x:c>
       <x:c r="D29" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -1196,7 +1196,7 @@
         </is>
       </x:c>
       <x:c r="C2">
-        <x:v>65</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="D2" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -1217,10 +1217,8 @@
           <t>Damage</t>
         </is>
       </x:c>
-      <x:c r="C3" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>100</t>
-        </is>
+      <x:c r="C3">
+        <x:v>300</x:v>
       </x:c>
       <x:c r="D3"/>
       <x:c r="E3" t="inlineStr">
@@ -1301,10 +1299,8 @@
           <t>Heal</t>
         </is>
       </x:c>
-      <x:c r="C7" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>40</t>
-        </is>
+      <x:c r="C7">
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D7" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -1325,10 +1321,8 @@
           <t>Shield</t>
         </is>
       </x:c>
-      <x:c r="C8" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>80</t>
-        </is>
+      <x:c r="C8">
+        <x:v>250</x:v>
       </x:c>
       <x:c r="D8" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -1470,7 +1464,7 @@
         </is>
       </x:c>
       <x:c r="C16">
-        <x:v>80</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="D16"/>
       <x:c r="E16" t="inlineStr">
@@ -1611,10 +1605,8 @@
           <t>Damage</t>
         </is>
       </x:c>
-      <x:c r="C23" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>40</t>
-        </is>
+      <x:c r="C23">
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D23"/>
       <x:c r="E23" t="inlineStr">
@@ -1820,10 +1812,8 @@
           <t>Timed</t>
         </is>
       </x:c>
-      <x:c r="D2" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>6</t>
-        </is>
+      <x:c r="D2">
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E2" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -1852,10 +1842,8 @@
           <t>Timed</t>
         </is>
       </x:c>
-      <x:c r="D3" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>6</t>
-        </is>
+      <x:c r="D3">
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E3" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -1884,10 +1872,8 @@
           <t>Timed</t>
         </is>
       </x:c>
-      <x:c r="D4" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>6</t>
-        </is>
+      <x:c r="D4">
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E4" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -1916,10 +1902,8 @@
           <t>Timed</t>
         </is>
       </x:c>
-      <x:c r="D5" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>6</t>
-        </is>
+      <x:c r="D5">
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E5" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -1948,10 +1932,8 @@
           <t>Timed</t>
         </is>
       </x:c>
-      <x:c r="D6" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>5</t>
-        </is>
+      <x:c r="D6">
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E6" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -1980,10 +1962,8 @@
           <t>Timed</t>
         </is>
       </x:c>
-      <x:c r="D7" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>6</t>
-        </is>
+      <x:c r="D7">
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E7" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -2012,10 +1992,8 @@
           <t>Timed</t>
         </is>
       </x:c>
-      <x:c r="D8" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>6</t>
-        </is>
+      <x:c r="D8">
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E8" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -2044,10 +2022,8 @@
           <t>Timed</t>
         </is>
       </x:c>
-      <x:c r="D9" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>6</t>
-        </is>
+      <x:c r="D9">
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E9" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -2076,10 +2052,8 @@
           <t>Timed</t>
         </is>
       </x:c>
-      <x:c r="D11" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>6</t>
-        </is>
+      <x:c r="D11">
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E11" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -2108,10 +2082,8 @@
           <t>Timed</t>
         </is>
       </x:c>
-      <x:c r="D12" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>6</t>
-        </is>
+      <x:c r="D12">
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E12" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -2140,10 +2112,8 @@
           <t>Timed</t>
         </is>
       </x:c>
-      <x:c r="D13" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>5</t>
-        </is>
+      <x:c r="D13">
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E13" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -2172,10 +2142,8 @@
           <t>Timed</t>
         </is>
       </x:c>
-      <x:c r="D14" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>1</t>
-        </is>
+      <x:c r="D14">
+        <x:v>1.25</x:v>
       </x:c>
       <x:c r="E14" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -2204,10 +2172,8 @@
           <t>Timed</t>
         </is>
       </x:c>
-      <x:c r="D15" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>2</t>
-        </is>
+      <x:c r="D15">
+        <x:v>2.5</x:v>
       </x:c>
       <x:c r="E15" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -2236,10 +2202,8 @@
           <t>Timed</t>
         </is>
       </x:c>
-      <x:c r="D16" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>6</t>
-        </is>
+      <x:c r="D16">
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E16" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -2268,10 +2232,8 @@
           <t>Timed</t>
         </is>
       </x:c>
-      <x:c r="D17" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>1.5</t>
-        </is>
+      <x:c r="D17">
+        <x:v>2.5</x:v>
       </x:c>
       <x:c r="E17" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -2300,10 +2262,8 @@
           <t>Timed</t>
         </is>
       </x:c>
-      <x:c r="D18" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>5</t>
-        </is>
+      <x:c r="D18">
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E18" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -2332,10 +2292,8 @@
           <t>Timed</t>
         </is>
       </x:c>
-      <x:c r="D19" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>5</t>
-        </is>
+      <x:c r="D19">
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E19" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -2364,10 +2322,8 @@
           <t>Timed</t>
         </is>
       </x:c>
-      <x:c r="D20" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>4</t>
-        </is>
+      <x:c r="D20">
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E20" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -2396,10 +2352,8 @@
           <t>Timed</t>
         </is>
       </x:c>
-      <x:c r="D21" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>5</t>
-        </is>
+      <x:c r="D21">
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E21" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -2428,10 +2382,8 @@
           <t>Timed</t>
         </is>
       </x:c>
-      <x:c r="D22" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>1</t>
-        </is>
+      <x:c r="D22">
+        <x:v>1.25</x:v>
       </x:c>
       <x:c r="E22" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -2460,10 +2412,8 @@
           <t>Timed</t>
         </is>
       </x:c>
-      <x:c r="D23" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>6</t>
-        </is>
+      <x:c r="D23">
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E23" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -2554,10 +2504,8 @@
           <t>Percent</t>
         </is>
       </x:c>
-      <x:c r="E2" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>0.1</t>
-        </is>
+      <x:c r="E2">
+        <x:v>0.15</x:v>
       </x:c>
       <x:c r="F2"/>
       <x:c r="G2"/>
@@ -2584,7 +2532,7 @@
         </is>
       </x:c>
       <x:c r="E3">
-        <x:v>-0.12</x:v>
+        <x:v>-0.2</x:v>
       </x:c>
       <x:c r="F3"/>
       <x:c r="G3"/>
@@ -2603,7 +2551,7 @@
       <x:c r="C4"/>
       <x:c r="D4"/>
       <x:c r="E4">
-        <x:v>0.02</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="F4" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -2629,12 +2577,12 @@
         </is>
       </x:c>
       <x:c r="D5" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>Percent</t>
-        </is>
+        <x:is>
+          <x:t>Flat</x:t>
+        </x:is>
       </x:c>
       <x:c r="E5">
-        <x:v>0.15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F5"/>
       <x:c r="G5"/>
@@ -2661,7 +2609,7 @@
         </is>
       </x:c>
       <x:c r="E6">
-        <x:v>-0.08</x:v>
+        <x:v>-0.18</x:v>
       </x:c>
       <x:c r="F6"/>
       <x:c r="G6"/>
@@ -2687,10 +2635,8 @@
           <t>Percent</t>
         </is>
       </x:c>
-      <x:c r="E7" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>0.1</t>
-        </is>
+      <x:c r="E7">
+        <x:v>0.15</x:v>
       </x:c>
       <x:c r="F7"/>
       <x:c r="G7"/>
@@ -2716,10 +2662,8 @@
           <t>Flat</t>
         </is>
       </x:c>
-      <x:c r="E8" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>0.08</t>
-        </is>
+      <x:c r="E8">
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="F8"/>
       <x:c r="G8"/>
@@ -2745,10 +2689,8 @@
           <t>Flat</t>
         </is>
       </x:c>
-      <x:c r="E9" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>0.08</t>
-        </is>
+      <x:c r="E9">
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="F9"/>
       <x:c r="G9"/>
@@ -2774,10 +2716,8 @@
           <t>Percent</t>
         </is>
       </x:c>
-      <x:c r="E11" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>0.15</t>
-        </is>
+      <x:c r="E11">
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="F11"/>
       <x:c r="G11"/>
@@ -2803,10 +2743,8 @@
           <t>Percent</t>
         </is>
       </x:c>
-      <x:c r="E12" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>-0.2</t>
-        </is>
+      <x:c r="E12">
+        <x:v>-0.35</x:v>
       </x:c>
       <x:c r="F12"/>
       <x:c r="G12"/>
@@ -2833,7 +2771,7 @@
         </is>
       </x:c>
       <x:c r="E13">
-        <x:v>-0.18</x:v>
+        <x:v>-0.3</x:v>
       </x:c>
       <x:c r="F13"/>
       <x:c r="G13"/>
@@ -2894,7 +2832,7 @@
       <x:c r="C16"/>
       <x:c r="D16"/>
       <x:c r="E16">
-        <x:v>12</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F16" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -2945,10 +2883,8 @@
           <t>Percent</t>
         </is>
       </x:c>
-      <x:c r="E18" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>-0.1</t>
-        </is>
+      <x:c r="E18">
+        <x:v>-0.15</x:v>
       </x:c>
       <x:c r="F18"/>
       <x:c r="G18"/>
@@ -2974,10 +2910,8 @@
           <t>Percent</t>
         </is>
       </x:c>
-      <x:c r="E19" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>-0.1</t>
-        </is>
+      <x:c r="E19">
+        <x:v>-0.2</x:v>
       </x:c>
       <x:c r="F19"/>
       <x:c r="G19"/>
@@ -3003,10 +2937,8 @@
           <t>Percent</t>
         </is>
       </x:c>
-      <x:c r="E20" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>-0.15</t>
-        </is>
+      <x:c r="E20">
+        <x:v>-0.25</x:v>
       </x:c>
       <x:c r="F20"/>
       <x:c r="G20"/>
@@ -3032,10 +2964,8 @@
           <t>Percent</t>
         </is>
       </x:c>
-      <x:c r="E21" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>-0.1</t>
-        </is>
+      <x:c r="E21">
+        <x:v>-0.15</x:v>
       </x:c>
       <x:c r="F21"/>
       <x:c r="G21"/>
@@ -3074,10 +3004,8 @@
       </x:c>
       <x:c r="C23"/>
       <x:c r="D23"/>
-      <x:c r="E23" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>10</t>
-        </is>
+      <x:c r="E23">
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F23" t="inlineStr">
         <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
